--- a/Career Planning.xlsx
+++ b/Career Planning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brad_\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB94130-FC42-41D4-9F2C-409693F81284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{284654F7-EA74-4E3E-B9CE-D640FBB07571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{CB356D7A-17D0-4CB7-939E-E66B980375A3}"/>
+    <workbookView xWindow="5610" yWindow="2920" windowWidth="28800" windowHeight="15370" activeTab="7" xr2:uid="{CB356D7A-17D0-4CB7-939E-E66B980375A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Version" sheetId="6" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="278">
   <si>
     <t>July</t>
   </si>
@@ -757,89 +757,116 @@
     <t>https://github.com/bvoris</t>
   </si>
   <si>
-    <t>Brad started his career in Information Technology and Cyber Security in 1999. He has numerous certifications including his CISSP, CISM, CCSK, NSE-1, NSE-2, MCP, and Network+ among many others. 
+    <t>Discord Channel:</t>
+  </si>
+  <si>
+    <t>https://discord.gg/u2TwuRgr36</t>
+  </si>
+  <si>
+    <t>Do not edit this page</t>
+  </si>
+  <si>
+    <t>Introduction</t>
+  </si>
+  <si>
+    <t>Summary: My brief introduction and mediums for connectivity.</t>
+  </si>
+  <si>
+    <t>Twitter Page:</t>
+  </si>
+  <si>
+    <t>https://twitter.com/HMInfoSecViking</t>
+  </si>
+  <si>
+    <t>How do I fill this out?</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>Page</t>
+  </si>
+  <si>
+    <t>Do not edit anything</t>
+  </si>
+  <si>
+    <t>How To</t>
+  </si>
+  <si>
+    <t>Context to modify</t>
+  </si>
+  <si>
+    <t>Fill out areas in current role, short term 1-3 years, long term 3-10 years</t>
+  </si>
+  <si>
+    <t>Fill out areas for will you persue further academic education, and cost (these can be estimates)</t>
+  </si>
+  <si>
+    <t>Goal Outline</t>
+  </si>
+  <si>
+    <t>What do you want to accomplish?</t>
+  </si>
+  <si>
+    <t>Fill out areas under What do you want to do, color code the area corresponding to what you want to do by the date you want to complete it.</t>
+  </si>
+  <si>
+    <t>Cyber Seek Career Pathway</t>
+  </si>
+  <si>
+    <t>https://www.cyberseek.org/pathway.html</t>
+  </si>
+  <si>
+    <t>CyberSecurity Guide</t>
+  </si>
+  <si>
+    <t>https://cybersecurityguide.org/careers/</t>
+  </si>
+  <si>
+    <t>For an instruction guide go here:</t>
+  </si>
+  <si>
+    <t>https://bvoris.github.io/content/career%20planning%20guide/2022/05/03/careerplanningguide/</t>
+  </si>
+  <si>
+    <t>Information Technology: Data Science (machine learning, artificial intelligence, etc.)</t>
+  </si>
+  <si>
+    <t>Microsoft Virtual Days Free Training</t>
+  </si>
+  <si>
+    <t>https://www.microsoft.com/en-us/trainingdays/</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/training/</t>
+  </si>
+  <si>
+    <t>Microsoft Training</t>
+  </si>
+  <si>
+    <t>4.0.4</t>
+  </si>
+  <si>
+    <t>Brad started his career in Information Technology and Cyber Security in 1999. He has numerous certifications including his CISSP, CISM, CCSP, CCSK, TAISE, NSE-1, NSE-2, MCP, and Network+ among many others. 
 Over his career he has worked with enterprise organizations like United Airlines, JP Morgan Chase, Texas Children’s Hospital and Walmart eCommerce. Brad is a U.S. Army Veteran.</t>
   </si>
   <si>
-    <t>Discord Channel:</t>
-  </si>
-  <si>
-    <t>https://discord.gg/u2TwuRgr36</t>
-  </si>
-  <si>
-    <t>Do not edit this page</t>
-  </si>
-  <si>
-    <t>Introduction</t>
-  </si>
-  <si>
-    <t>Summary: My brief introduction and mediums for connectivity.</t>
-  </si>
-  <si>
-    <t>Twitter Page:</t>
-  </si>
-  <si>
-    <t>https://twitter.com/HMInfoSecViking</t>
-  </si>
-  <si>
-    <t>How do I fill this out?</t>
-  </si>
-  <si>
-    <t>Version</t>
-  </si>
-  <si>
-    <t>Page</t>
-  </si>
-  <si>
-    <t>Do not edit anything</t>
-  </si>
-  <si>
-    <t>How To</t>
-  </si>
-  <si>
-    <t>Context to modify</t>
-  </si>
-  <si>
-    <t>Fill out areas in current role, short term 1-3 years, long term 3-10 years</t>
-  </si>
-  <si>
-    <t>Fill out areas for will you persue further academic education, and cost (these can be estimates)</t>
-  </si>
-  <si>
-    <t>Goal Outline</t>
-  </si>
-  <si>
-    <t>What do you want to accomplish?</t>
-  </si>
-  <si>
-    <t>Fill out areas under What do you want to do, color code the area corresponding to what you want to do by the date you want to complete it.</t>
-  </si>
-  <si>
-    <t>Cyber Seek Career Pathway</t>
-  </si>
-  <si>
-    <t>https://www.cyberseek.org/pathway.html</t>
-  </si>
-  <si>
-    <t>CyberSecurity Guide</t>
-  </si>
-  <si>
-    <t>https://cybersecurityguide.org/careers/</t>
-  </si>
-  <si>
-    <t>For an instruction guide go here:</t>
-  </si>
-  <si>
-    <t>https://bvoris.github.io/content/career%20planning%20guide/2022/05/03/careerplanningguide/</t>
-  </si>
-  <si>
-    <t>Information Technology: Data Science (machine learning, artificial intelligence, etc.)</t>
-  </si>
-  <si>
-    <t>Microsoft Virtual Days Free Training</t>
-  </si>
-  <si>
-    <t>https://www.microsoft.com/en-us/trainingdays/</t>
+    <t>AWS Training</t>
+  </si>
+  <si>
+    <t>https://aws.training</t>
+  </si>
+  <si>
+    <t>https://www.cisco.com/site/us/en/learn/training-certifications/training/netacad/index.html</t>
+  </si>
+  <si>
+    <t>Cisco Training</t>
+  </si>
+  <si>
+    <t>Google Cloud Platform</t>
+  </si>
+  <si>
+    <t>https://cloud.google.com/learn/training</t>
   </si>
 </sst>
 </file>
@@ -1426,8 +1453,8 @@
       <c r="A3" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="B3" s="20">
-        <v>4.03</v>
+      <c r="B3" s="20" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -1435,7 +1462,7 @@
         <v>232</v>
       </c>
       <c r="B4" s="21">
-        <v>45358</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1463,39 +1490,39 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="14" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -1503,7 +1530,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -1511,7 +1538,7 @@
         <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -1519,15 +1546,15 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -1535,17 +1562,17 @@
         <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -1567,12 +1594,12 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="14" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="17" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -1594,7 +1621,7 @@
         <v>236</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -1618,24 +1645,24 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>247</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>242</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="5"/>
       <c r="B12" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -2341,7 +2368,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="15" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
@@ -3202,10 +3229,10 @@
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B5" s="23">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C5" s="24"/>
       <c r="D5" s="24"/>
@@ -3219,7 +3246,7 @@
       <c r="L5" s="24"/>
       <c r="M5" s="25"/>
       <c r="N5" s="23">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="O5" s="24"/>
       <c r="P5" s="24"/>
@@ -3233,7 +3260,7 @@
       <c r="X5" s="24"/>
       <c r="Y5" s="25"/>
       <c r="Z5" s="23">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="AA5" s="24"/>
       <c r="AB5" s="24"/>
@@ -3482,7 +3509,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64FCAB0A-CF34-4155-AC2A-718F62C76466}">
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A39"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" ht="18.5" x14ac:dyDescent="0.45">
@@ -3555,32 +3582,72 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="16" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29" s="5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30" s="16" t="s">
         <v>268</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A32" s="5" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" s="16" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" s="5" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" s="16" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" s="5" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" s="16" t="s">
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -3594,8 +3661,12 @@
     <hyperlink ref="A21" r:id="rId7" xr:uid="{538CA7A3-D66B-4AB5-8721-C3ACC7336AEB}"/>
     <hyperlink ref="A24" r:id="rId8" xr:uid="{4F607F03-7CA4-4993-857C-57BCFA452427}"/>
     <hyperlink ref="A27" r:id="rId9" xr:uid="{E55E5472-F821-461D-A568-ACCB995B0DBB}"/>
+    <hyperlink ref="A30" r:id="rId10" xr:uid="{399D1068-1DC7-4005-B14B-9912059B32E4}"/>
+    <hyperlink ref="A33" r:id="rId11" xr:uid="{C53CC3F3-CEAD-4CF6-AFD2-6C67B3DA2C34}"/>
+    <hyperlink ref="A36" r:id="rId12" xr:uid="{70571476-F977-4255-94A2-F499A1D81099}"/>
+    <hyperlink ref="A39" r:id="rId13" xr:uid="{C70B79A8-3CF5-412E-B55C-5A95CAB427F2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId10"/>
+  <pageSetup orientation="portrait" r:id="rId14"/>
 </worksheet>
 </file>